--- a/backend/sample_bulk_students_corrected.xlsx
+++ b/backend/sample_bulk_students_corrected.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hp\Desktop\UPASS\backend\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\KHOSMOS\Desktop\testing_upass\backend\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_E82743355918F863686002FA60D6B0DFA12C4B2E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D921489-EB5E-4DB6-ADAD-579FEBFB81AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="360" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Students" sheetId="1" r:id="rId1"/>
@@ -665,10 +665,18 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="12"/>
+      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -691,13 +699,16 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -1036,7 +1047,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F61"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="25.796875" customWidth="1"/>
     <col min="2" max="2" width="20.796875" customWidth="1"/>
@@ -1045,7 +1056,7 @@
     <col min="6" max="6" width="15.796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1065,7 +1076,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -1085,7 +1096,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -1105,7 +1116,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>18</v>
       </c>
@@ -1125,7 +1136,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>23</v>
       </c>
@@ -1145,7 +1156,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>28</v>
       </c>
@@ -1165,7 +1176,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>33</v>
       </c>
@@ -1185,7 +1196,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>38</v>
       </c>
@@ -1205,7 +1216,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>43</v>
       </c>
@@ -1225,7 +1236,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>48</v>
       </c>
@@ -1245,7 +1256,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>53</v>
       </c>
@@ -1265,7 +1276,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>58</v>
       </c>
@@ -1285,7 +1296,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>61</v>
       </c>
@@ -1305,7 +1316,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="14" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>65</v>
       </c>
@@ -1325,7 +1336,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="15" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>68</v>
       </c>
@@ -1345,7 +1356,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="16" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>71</v>
       </c>
@@ -1365,7 +1376,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="17" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>74</v>
       </c>
@@ -1385,7 +1396,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="18" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>78</v>
       </c>
@@ -1405,7 +1416,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="19" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>81</v>
       </c>
@@ -1425,7 +1436,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="20" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>84</v>
       </c>
@@ -1445,7 +1456,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="21" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>88</v>
       </c>
@@ -1465,7 +1476,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="22" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>92</v>
       </c>
@@ -1485,7 +1496,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="23" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>95</v>
       </c>
@@ -1505,7 +1516,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="24" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>98</v>
       </c>
@@ -1525,7 +1536,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="25" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>101</v>
       </c>
@@ -1545,7 +1556,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="26" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>104</v>
       </c>
@@ -1565,7 +1576,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="27" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>107</v>
       </c>
@@ -1585,7 +1596,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="28" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>111</v>
       </c>
@@ -1605,7 +1616,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="29" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>114</v>
       </c>
@@ -1625,7 +1636,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="30" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>117</v>
       </c>
@@ -1645,7 +1656,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="31" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>121</v>
       </c>
@@ -1665,7 +1676,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="32" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>124</v>
       </c>
@@ -1685,7 +1696,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="33" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>127</v>
       </c>
@@ -1705,7 +1716,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="34" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>130</v>
       </c>
@@ -1725,7 +1736,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="35" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>133</v>
       </c>
@@ -1745,7 +1756,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="36" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>136</v>
       </c>
@@ -1765,7 +1776,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="37" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>139</v>
       </c>
@@ -1785,7 +1796,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="38" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>142</v>
       </c>
@@ -1805,7 +1816,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="39" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>145</v>
       </c>
@@ -1825,7 +1836,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="40" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>148</v>
       </c>
@@ -1845,7 +1856,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="41" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>151</v>
       </c>
@@ -1865,7 +1876,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="42" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>154</v>
       </c>
@@ -1885,7 +1896,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="43" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>157</v>
       </c>
@@ -1905,7 +1916,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="44" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>160</v>
       </c>
@@ -1925,7 +1936,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="45" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>163</v>
       </c>
@@ -1945,7 +1956,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="46" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>166</v>
       </c>
@@ -1965,7 +1976,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="47" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>169</v>
       </c>
@@ -1985,7 +1996,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="48" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>74</v>
       </c>
@@ -2005,7 +2016,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="49" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>174</v>
       </c>
@@ -2025,7 +2036,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="50" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>177</v>
       </c>
@@ -2045,7 +2056,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="51" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>180</v>
       </c>
@@ -2065,7 +2076,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="52" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>183</v>
       </c>
@@ -2085,7 +2096,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="53" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>186</v>
       </c>
@@ -2105,7 +2116,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="54" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>189</v>
       </c>
@@ -2125,7 +2136,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="55" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>192</v>
       </c>
@@ -2145,7 +2156,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="56" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>195</v>
       </c>
@@ -2165,7 +2176,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="57" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>198</v>
       </c>
@@ -2185,7 +2196,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="58" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>201</v>
       </c>
@@ -2205,7 +2216,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="59" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>204</v>
       </c>
@@ -2225,7 +2236,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="60" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>207</v>
       </c>
@@ -2245,14 +2256,14 @@
         <v>11</v>
       </c>
     </row>
-    <row r="61" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>210</v>
       </c>
       <c r="B61" t="s">
         <v>211</v>
       </c>
-      <c r="C61" t="s">
+      <c r="C61" s="1" t="s">
         <v>212</v>
       </c>
       <c r="D61" t="s">
@@ -2266,9 +2277,12 @@
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="C61" r:id="rId1" xr:uid="{E26FD4F2-DD43-4A46-A9FE-858ABD17AA6A}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:F61" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:F60 A61:B61 D61:F61" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>